--- a/words.xlsx
+++ b/words.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C45FC5BD-AE57-A640-94AB-E7CFE72F2566}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7167C44B-93E3-F249-B047-6F078DBEC44D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="460" windowWidth="24820" windowHeight="15020" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>word</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -71,6 +71,10 @@
   </si>
   <si>
     <t>鸡蛋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>day</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -435,55 +439,73 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{527ABE91-7216-BA4F-A91C-2F06E544A41C}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
       </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
       </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
